--- a/Matrix.xlsx
+++ b/Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anoopmadhavan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{03B7954B-6F19-654B-BC27-5C58A30A7632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8F2DD4-D1D9-FA44-A134-00BD9C3994A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{4AF06BF6-F7A6-AE4F-A7FC-E899F9A61833}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19380" xr2:uid="{4AF06BF6-F7A6-AE4F-A7FC-E899F9A61833}"/>
   </bookViews>
   <sheets>
     <sheet name="Credibility_Matrix_Ramesh_Chand" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -607,6 +607,12 @@
       <b/>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
       <name val="Cambria"/>
       <family val="1"/>
     </font>
@@ -973,7 +979,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -982,6 +988,10 @@
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1361,12 +1371,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="30" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" style="2" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" style="2" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" style="2" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" style="2" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="2" customWidth="1"/>
     <col min="5" max="6" width="39.83203125" style="2" customWidth="1"/>
     <col min="7" max="8" width="20.83203125" style="2" customWidth="1"/>
     <col min="9" max="16384" width="10.83203125" style="2"/>
@@ -1399,7 +1409,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="97" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1424,8 +1434,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+    <row r="3" spans="1:8" ht="238" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1451,7 +1461,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="357" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1477,7 +1487,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="179" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1502,8 +1512,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+    <row r="6" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1529,7 +1539,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="148" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1555,7 +1565,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="179" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1580,8 +1590,8 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+    <row r="9" spans="1:8" ht="136" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1606,8 +1616,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+    <row r="10" spans="1:8" ht="204" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1632,8 +1642,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+    <row r="11" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1658,8 +1668,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+    <row r="12" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1685,7 +1695,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1710,8 +1720,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="136" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+    <row r="14" spans="1:8" ht="187" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1736,8 +1746,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+    <row r="15" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1762,8 +1772,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+    <row r="16" spans="1:8" ht="136" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1788,8 +1798,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="136" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+    <row r="17" spans="1:8" ht="204" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1814,8 +1824,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+    <row r="18" spans="1:8" ht="170" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1840,9 +1850,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>20</v>
+    <row r="19" spans="1:8" ht="187" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>133</v>
@@ -1866,9 +1876,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="85" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>21</v>
+    <row r="20" spans="1:8" ht="136" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>133</v>
@@ -1893,8 +1903,8 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="100" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>22</v>
+      <c r="A21" s="4">
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>133</v>
@@ -1918,61 +1928,61 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>23</v>
+    <row r="22" spans="1:8" ht="136" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>24</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="119" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>25</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="170" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>134</v>
@@ -1981,104 +1991,104 @@
         <v>54</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>26</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="153" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>28</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="119" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="102" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>29</v>
+      <c r="A27" s="4">
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H29">
-    <sortCondition ref="A2:A29"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H28">
+    <sortCondition ref="A2:A28"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup scale="72" fitToHeight="10" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup scale="82" fitToHeight="10" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>